--- a/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
@@ -157,7 +157,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Philippines power generation by fuel (IEMOP WESM schedules; geothermal in Other) (to Oct/26)</a:t>
+              <a:t>Philippines power generation by fuel (IEMOP WESM schedules; geothermal in Other) (to Sep/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -187,12 +187,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$5</f>
+              <f>'Chart'!$B$2:$B$4</f>
             </numRef>
           </val>
         </ser>
@@ -215,12 +215,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$5</f>
+              <f>'Chart'!$C$2:$C$4</f>
             </numRef>
           </val>
         </ser>
@@ -243,12 +243,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$5</f>
+              <f>'Chart'!$D$2:$D$4</f>
             </numRef>
           </val>
         </ser>
@@ -271,12 +271,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$5</f>
+              <f>'Chart'!$E$2:$E$4</f>
             </numRef>
           </val>
         </ser>
@@ -299,12 +299,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$5</f>
+              <f>'Chart'!$F$2:$F$4</f>
             </numRef>
           </val>
         </ser>
@@ -327,12 +327,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$5</f>
+              <f>'Chart'!$G$2:$G$4</f>
             </numRef>
           </val>
         </ser>
@@ -355,12 +355,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$5</f>
+              <f>'Chart'!$A$2:$A$4</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$5</f>
+              <f>'Chart'!$H$2:$H$4</f>
             </numRef>
           </val>
         </ser>
@@ -1057,7 +1057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1181,32 +1181,6 @@
       </c>
       <c r="H4" t="n">
         <v>1118.6604</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="n">
-        <v>46296</v>
-      </c>
-      <c r="B5" t="n">
-        <v>115.1419</v>
-      </c>
-      <c r="C5" t="n">
-        <v>201.6049</v>
-      </c>
-      <c r="D5" t="n">
-        <v>3.2096</v>
-      </c>
-      <c r="E5" t="n">
-        <v>96.0294</v>
-      </c>
-      <c r="F5" t="n">
-        <v>573.0456999999999</v>
-      </c>
-      <c r="G5" t="n">
-        <v>0</v>
-      </c>
-      <c r="H5" t="n">
-        <v>105.8152</v>
       </c>
     </row>
   </sheetData>

--- a/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="166" formatCode="mmm/yy"/>
+    <numFmt numFmtId="165" formatCode="mmm/yy"/>
+    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,12 +63,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -157,6 +158,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Philippines power generation by fuel (IEMOP WESM schedules; geothermal in Other) (to Sep/26)</a:t>
             </a:r>
           </a:p>
@@ -460,6 +462,7 @@
               <a:defRPr/>
             </a:pPr>
             <a:r>
+              <a:rPr sz="1200" b="1"/>
               <a:t>Philippines WESM demand (IEMOP) (to Oct/26)</a:t>
             </a:r>
           </a:p>
@@ -1001,7 +1004,6 @@
         </is>
       </c>
     </row>
-    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1016,7 +1018,6 @@
         </is>
       </c>
     </row>
-    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1031,7 +1032,6 @@
         </is>
       </c>
     </row>
-    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -1106,7 +1106,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -1132,7 +1132,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B3" t="n">
@@ -1158,7 +1158,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B4" t="n">
@@ -1174,7 +1174,7 @@
         <v>804.7102</v>
       </c>
       <c r="F4" t="n">
-        <v>5453.9455</v>
+        <v>5453.945499999999</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
@@ -1219,7 +1219,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="5" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -1230,7 +1230,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="5" t="n">
         <v>46235</v>
       </c>
       <c r="B3" t="n">
@@ -1241,7 +1241,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="5" t="n">
         <v>46266</v>
       </c>
       <c r="B4" t="n">
@@ -1252,7 +1252,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="5" t="n">
         <v>46296</v>
       </c>
       <c r="B5" t="n">

--- a/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
+++ b/output/Data and Chart Outputs/philippines_power_generation_daily.xlsx
@@ -22,8 +22,8 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="3">
     <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="mmm/yy"/>
-    <numFmt numFmtId="166" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="166" formatCode="mmm/yy"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -63,13 +63,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -159,7 +158,7 @@
             </a:pPr>
             <a:r>
               <a:rPr sz="1200" b="1"/>
-              <a:t>Philippines power generation by fuel (IEMOP WESM schedules; geothermal in Other) (to Sep/26)</a:t>
+              <a:t>Philippines power generation by fuel (IEMOP WESM schedules; geothermal in Other) (to Oct/26)</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -189,12 +188,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$B$2:$B$4</f>
+              <f>'Chart'!$B$2:$B$5</f>
             </numRef>
           </val>
         </ser>
@@ -217,12 +216,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$C$2:$C$4</f>
+              <f>'Chart'!$C$2:$C$5</f>
             </numRef>
           </val>
         </ser>
@@ -245,12 +244,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$D$2:$D$4</f>
+              <f>'Chart'!$D$2:$D$5</f>
             </numRef>
           </val>
         </ser>
@@ -273,12 +272,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$E$2:$E$4</f>
+              <f>'Chart'!$E$2:$E$5</f>
             </numRef>
           </val>
         </ser>
@@ -301,12 +300,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$F$2:$F$4</f>
+              <f>'Chart'!$F$2:$F$5</f>
             </numRef>
           </val>
         </ser>
@@ -329,12 +328,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$G$2:$G$4</f>
+              <f>'Chart'!$G$2:$G$5</f>
             </numRef>
           </val>
         </ser>
@@ -357,12 +356,12 @@
           </spPr>
           <cat>
             <numRef>
-              <f>'Chart'!$A$2:$A$4</f>
+              <f>'Chart'!$A$2:$A$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Chart'!$H$2:$H$4</f>
+              <f>'Chart'!$H$2:$H$5</f>
             </numRef>
           </val>
         </ser>
@@ -1004,6 +1003,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
@@ -1018,6 +1018,7 @@
         </is>
       </c>
     </row>
+    <row r="8"/>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
@@ -1028,10 +1029,11 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>From 2026-07-06 to 2026-10-03; final (DIPCEF) data for 51 days, raw (DIPCER) for the rest. Grid-connected WESM regions only (Luzon, Visayas, Mindanao); off-grid islands (Mindoro, Palawan, etc.) and embedded generation that is not scheduled in WESM (rooftop solar, small plants inside distribution networks) are not included. Scheduled, not metered, generation: the dispatch target for each 5-minute interval. IEMOP lists about 90 days of files; older days are kept from previous runs.</t>
-        </is>
-      </c>
-    </row>
+          <t>From 2026-07-06 to 2026-10-27; final (DIPCEF) data for 82 days, raw (DIPCER) for the rest. Grid-connected WESM regions only (Luzon, Visayas, Mindanao); off-grid islands (Mindoro, Palawan, etc.) and embedded generation that is not scheduled in WESM (rooftop solar, small plants inside distribution networks) are not included. Scheduled, not metered, generation: the dispatch target for each 5-minute interval. IEMOP lists about 90 days of files; older days are kept from previous runs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11"/>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
@@ -1057,7 +1059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -1106,7 +1108,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -1132,55 +1134,81 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B3" t="n">
-        <v>1083.9053</v>
+        <v>1083.9041</v>
       </c>
       <c r="C3" t="n">
         <v>1598.92</v>
       </c>
       <c r="D3" t="n">
-        <v>150.0491</v>
+        <v>150.0502</v>
       </c>
       <c r="E3" t="n">
-        <v>552.4369</v>
+        <v>552.4094</v>
       </c>
       <c r="F3" t="n">
-        <v>5803.135200000001</v>
+        <v>5803.1328</v>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
       <c r="H3" t="n">
-        <v>1179.7454</v>
+        <v>1179.7414</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B4" t="n">
-        <v>1208.9</v>
+        <v>1208.9131</v>
       </c>
       <c r="C4" t="n">
         <v>1785.3388</v>
       </c>
       <c r="D4" t="n">
-        <v>65.7162</v>
+        <v>65.71680000000001</v>
       </c>
       <c r="E4" t="n">
-        <v>804.7102</v>
+        <v>804.6009999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>5453.945499999999</v>
+        <v>5453.9311</v>
       </c>
       <c r="G4" t="n">
         <v>0</v>
       </c>
       <c r="H4" t="n">
-        <v>1118.6604</v>
+        <v>1118.7498</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="3" t="n">
+        <v>46296</v>
+      </c>
+      <c r="B5" t="n">
+        <v>870.8314</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1654.2549</v>
+      </c>
+      <c r="D5" t="n">
+        <v>94.22030000000001</v>
+      </c>
+      <c r="E5" t="n">
+        <v>841.13</v>
+      </c>
+      <c r="F5" t="n">
+        <v>5316.960700000001</v>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>958.0017999999999</v>
       </c>
     </row>
   </sheetData>
@@ -1219,7 +1247,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="5" t="n">
+      <c r="A2" s="3" t="n">
         <v>46204</v>
       </c>
       <c r="B2" t="n">
@@ -1230,7 +1258,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="5" t="n">
+      <c r="A3" s="3" t="n">
         <v>46235</v>
       </c>
       <c r="B3" t="n">
@@ -1241,7 +1269,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="5" t="n">
+      <c r="A4" s="3" t="n">
         <v>46266</v>
       </c>
       <c r="B4" t="n">
@@ -1252,14 +1280,14 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="5" t="n">
+      <c r="A5" s="3" t="n">
         <v>46296</v>
       </c>
       <c r="B5" t="n">
-        <v>14781.9</v>
+        <v>14601.24074074074</v>
       </c>
       <c r="C5" t="n">
-        <v>17024.13333333333</v>
+        <v>16788.08518518518</v>
       </c>
     </row>
   </sheetData>
@@ -1274,7 +1302,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O91"/>
+  <dimension ref="A1:O115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3858,47 +3886,47 @@
         <v>46260</v>
       </c>
       <c r="B53" t="n">
-        <v>199324.8</v>
+        <v>199324.6</v>
       </c>
       <c r="C53" t="n">
         <v>54962.8</v>
       </c>
       <c r="D53" t="n">
-        <v>8888.700000000001</v>
+        <v>8889</v>
       </c>
       <c r="E53" t="n">
         <v>41107.2</v>
       </c>
       <c r="F53" t="n">
-        <v>26480.5</v>
+        <v>26468.9</v>
       </c>
       <c r="G53" t="n">
-        <v>5051.8</v>
+        <v>5052.5</v>
       </c>
       <c r="H53" t="n">
         <v>1790.7</v>
       </c>
       <c r="I53" t="n">
-        <v>29267.1</v>
+        <v>29267.8</v>
       </c>
       <c r="J53" t="n">
-        <v>366873.6</v>
+        <v>366863.5</v>
       </c>
       <c r="K53" t="n">
-        <v>28868.1</v>
+        <v>28868.5</v>
       </c>
       <c r="L53" t="n">
-        <v>284.4</v>
+        <v>283.4</v>
       </c>
       <c r="M53" t="n">
-        <v>114.6</v>
+        <v>115.9</v>
       </c>
       <c r="N53" t="n">
         <v>288</v>
       </c>
       <c r="O53" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -3907,47 +3935,47 @@
         <v>46261</v>
       </c>
       <c r="B54" t="n">
-        <v>199745.2</v>
+        <v>199744.7</v>
       </c>
       <c r="C54" t="n">
         <v>59992.5</v>
       </c>
       <c r="D54" t="n">
-        <v>7925.1</v>
+        <v>7931.4</v>
       </c>
       <c r="E54" t="n">
-        <v>39393.1</v>
+        <v>39393.2</v>
       </c>
       <c r="F54" t="n">
-        <v>18509.3</v>
+        <v>18500.5</v>
       </c>
       <c r="G54" t="n">
-        <v>6030.3</v>
+        <v>6030.6</v>
       </c>
       <c r="H54" t="n">
-        <v>1828.6</v>
+        <v>1828.7</v>
       </c>
       <c r="I54" t="n">
-        <v>28472.8</v>
+        <v>28473.1</v>
       </c>
       <c r="J54" t="n">
-        <v>361897</v>
+        <v>361894.7</v>
       </c>
       <c r="K54" t="n">
-        <v>28096.1</v>
+        <v>28095.5</v>
       </c>
       <c r="L54" t="n">
-        <v>275.8</v>
+        <v>272.9</v>
       </c>
       <c r="M54" t="n">
-        <v>100.9</v>
+        <v>104.7</v>
       </c>
       <c r="N54" t="n">
         <v>288</v>
       </c>
       <c r="O54" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -3956,19 +3984,19 @@
         <v>46262</v>
       </c>
       <c r="B55" t="n">
-        <v>190370.3</v>
+        <v>190369.9</v>
       </c>
       <c r="C55" t="n">
         <v>54358</v>
       </c>
       <c r="D55" t="n">
-        <v>7759</v>
+        <v>7760</v>
       </c>
       <c r="E55" t="n">
         <v>38262.6</v>
       </c>
       <c r="F55" t="n">
-        <v>12263.6</v>
+        <v>12263.5</v>
       </c>
       <c r="G55" t="n">
         <v>6414.9</v>
@@ -3977,26 +4005,26 @@
         <v>1888.3</v>
       </c>
       <c r="I55" t="n">
-        <v>28867.1</v>
+        <v>28866.3</v>
       </c>
       <c r="J55" t="n">
-        <v>340183.9</v>
+        <v>340183.5</v>
       </c>
       <c r="K55" t="n">
         <v>28423.1</v>
       </c>
       <c r="L55" t="n">
-        <v>370.2</v>
+        <v>369.3</v>
       </c>
       <c r="M55" t="n">
-        <v>73.8</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N55" t="n">
         <v>288</v>
       </c>
       <c r="O55" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4005,19 +4033,19 @@
         <v>46263</v>
       </c>
       <c r="B56" t="n">
-        <v>169021.5</v>
+        <v>169021</v>
       </c>
       <c r="C56" t="n">
         <v>50855.7</v>
       </c>
       <c r="D56" t="n">
-        <v>7826.6</v>
+        <v>7829.8</v>
       </c>
       <c r="E56" t="n">
-        <v>36614</v>
+        <v>36613</v>
       </c>
       <c r="F56" t="n">
-        <v>12600.4</v>
+        <v>12598.2</v>
       </c>
       <c r="G56" t="n">
         <v>5974.9</v>
@@ -4026,26 +4054,26 @@
         <v>1908.8</v>
       </c>
       <c r="I56" t="n">
-        <v>28475.7</v>
+        <v>28473.5</v>
       </c>
       <c r="J56" t="n">
-        <v>313277.5</v>
+        <v>313274.9</v>
       </c>
       <c r="K56" t="n">
-        <v>28059.9</v>
+        <v>28059.7</v>
       </c>
       <c r="L56" t="n">
-        <v>337.9</v>
+        <v>335.6</v>
       </c>
       <c r="M56" t="n">
-        <v>77.8</v>
+        <v>78.2</v>
       </c>
       <c r="N56" t="n">
         <v>288</v>
       </c>
       <c r="O56" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4054,47 +4082,47 @@
         <v>46264</v>
       </c>
       <c r="B57" t="n">
-        <v>147239.5</v>
+        <v>147239.2</v>
       </c>
       <c r="C57" t="n">
         <v>54824.3</v>
       </c>
       <c r="D57" t="n">
-        <v>6634.1</v>
+        <v>6633.1</v>
       </c>
       <c r="E57" t="n">
         <v>35405.6</v>
       </c>
       <c r="F57" t="n">
-        <v>13423.4</v>
+        <v>13421.9</v>
       </c>
       <c r="G57" t="n">
-        <v>3678.7</v>
+        <v>3679</v>
       </c>
       <c r="H57" t="n">
         <v>1839.5</v>
       </c>
       <c r="I57" t="n">
-        <v>28928.5</v>
+        <v>28927.9</v>
       </c>
       <c r="J57" t="n">
-        <v>291973.5</v>
+        <v>291970.6</v>
       </c>
       <c r="K57" t="n">
-        <v>28498.3</v>
+        <v>28498</v>
       </c>
       <c r="L57" t="n">
-        <v>351.7</v>
+        <v>351.3</v>
       </c>
       <c r="M57" t="n">
-        <v>78.40000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="N57" t="n">
         <v>288</v>
       </c>
       <c r="O57" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4103,47 +4131,47 @@
         <v>46265</v>
       </c>
       <c r="B58" t="n">
-        <v>155588.8</v>
+        <v>155588.3</v>
       </c>
       <c r="C58" t="n">
         <v>57300.9</v>
       </c>
       <c r="D58" t="n">
-        <v>7784.1</v>
+        <v>7789.2</v>
       </c>
       <c r="E58" t="n">
-        <v>34649.5</v>
+        <v>34649.2</v>
       </c>
       <c r="F58" t="n">
-        <v>19400.7</v>
+        <v>19397.4</v>
       </c>
       <c r="G58" t="n">
-        <v>5778.6</v>
+        <v>5778.4</v>
       </c>
       <c r="H58" t="n">
         <v>1671.6</v>
       </c>
       <c r="I58" t="n">
-        <v>29469.7</v>
+        <v>29453.3</v>
       </c>
       <c r="J58" t="n">
-        <v>311643.9</v>
+        <v>311628.3</v>
       </c>
       <c r="K58" t="n">
-        <v>28998.5</v>
+        <v>28998</v>
       </c>
       <c r="L58" t="n">
-        <v>393</v>
+        <v>376.6</v>
       </c>
       <c r="M58" t="n">
-        <v>78.2</v>
+        <v>78.7</v>
       </c>
       <c r="N58" t="n">
         <v>288</v>
       </c>
       <c r="O58" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4152,47 +4180,47 @@
         <v>46266</v>
       </c>
       <c r="B59" t="n">
-        <v>181450.5</v>
+        <v>181449.8</v>
       </c>
       <c r="C59" t="n">
         <v>57157.5</v>
       </c>
       <c r="D59" t="n">
-        <v>10503.7</v>
+        <v>10505.3</v>
       </c>
       <c r="E59" t="n">
         <v>41538.7</v>
       </c>
       <c r="F59" t="n">
-        <v>22475.1</v>
+        <v>22473.2</v>
       </c>
       <c r="G59" t="n">
-        <v>6561.1</v>
+        <v>6561.3</v>
       </c>
       <c r="H59" t="n">
         <v>1802.7</v>
       </c>
       <c r="I59" t="n">
-        <v>29873.6</v>
+        <v>29876.5</v>
       </c>
       <c r="J59" t="n">
-        <v>351362.9</v>
+        <v>351365</v>
       </c>
       <c r="K59" t="n">
-        <v>29306.6</v>
+        <v>29306.2</v>
       </c>
       <c r="L59" t="n">
-        <v>425.4</v>
+        <v>426.7</v>
       </c>
       <c r="M59" t="n">
-        <v>141.6</v>
+        <v>143.6</v>
       </c>
       <c r="N59" t="n">
         <v>288</v>
       </c>
       <c r="O59" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4201,47 +4229,47 @@
         <v>46267</v>
       </c>
       <c r="B60" t="n">
-        <v>191465.9</v>
+        <v>191471.5</v>
       </c>
       <c r="C60" t="n">
         <v>55370.5</v>
       </c>
       <c r="D60" t="n">
-        <v>10569.7</v>
+        <v>10591.5</v>
       </c>
       <c r="E60" t="n">
-        <v>41266.2</v>
+        <v>41276.6</v>
       </c>
       <c r="F60" t="n">
-        <v>23094.8</v>
+        <v>23091.3</v>
       </c>
       <c r="G60" t="n">
-        <v>6239.1</v>
+        <v>6238.9</v>
       </c>
       <c r="H60" t="n">
-        <v>1562.1</v>
+        <v>1562.2</v>
       </c>
       <c r="I60" t="n">
-        <v>30461.8</v>
+        <v>30462.1</v>
       </c>
       <c r="J60" t="n">
-        <v>360030</v>
+        <v>360064.6</v>
       </c>
       <c r="K60" t="n">
-        <v>29826.5</v>
+        <v>29826.8</v>
       </c>
       <c r="L60" t="n">
-        <v>460.3</v>
+        <v>458.3</v>
       </c>
       <c r="M60" t="n">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="N60" t="n">
         <v>288</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4250,19 +4278,19 @@
         <v>46268</v>
       </c>
       <c r="B61" t="n">
-        <v>194156.9</v>
+        <v>194156.6</v>
       </c>
       <c r="C61" t="n">
         <v>55177.6</v>
       </c>
       <c r="D61" t="n">
-        <v>11711.8</v>
+        <v>11714</v>
       </c>
       <c r="E61" t="n">
-        <v>40433.5</v>
+        <v>40436.1</v>
       </c>
       <c r="F61" t="n">
-        <v>21234.2</v>
+        <v>21227.3</v>
       </c>
       <c r="G61" t="n">
         <v>6544.2</v>
@@ -4271,26 +4299,26 @@
         <v>1585.7</v>
       </c>
       <c r="I61" t="n">
-        <v>30234.2</v>
+        <v>30233.9</v>
       </c>
       <c r="J61" t="n">
-        <v>361078.1</v>
+        <v>361075.4</v>
       </c>
       <c r="K61" t="n">
-        <v>29610.2</v>
+        <v>29610</v>
       </c>
       <c r="L61" t="n">
-        <v>425.8</v>
+        <v>425.2</v>
       </c>
       <c r="M61" t="n">
-        <v>198.1</v>
+        <v>198.7</v>
       </c>
       <c r="N61" t="n">
         <v>288</v>
       </c>
       <c r="O61" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4299,47 +4327,47 @@
         <v>46269</v>
       </c>
       <c r="B62" t="n">
-        <v>191810.7</v>
+        <v>191810.3</v>
       </c>
       <c r="C62" t="n">
         <v>55623.8</v>
       </c>
       <c r="D62" t="n">
-        <v>9781.9</v>
+        <v>9783.4</v>
       </c>
       <c r="E62" t="n">
-        <v>39684.9</v>
+        <v>39685</v>
       </c>
       <c r="F62" t="n">
-        <v>17424.4</v>
+        <v>17414</v>
       </c>
       <c r="G62" t="n">
-        <v>4582.1</v>
+        <v>4582.5</v>
       </c>
       <c r="H62" t="n">
         <v>1618.7</v>
       </c>
       <c r="I62" t="n">
-        <v>29949.1</v>
+        <v>29948.6</v>
       </c>
       <c r="J62" t="n">
-        <v>350475.5</v>
+        <v>350466.3</v>
       </c>
       <c r="K62" t="n">
-        <v>29033.1</v>
+        <v>29034.3</v>
       </c>
       <c r="L62" t="n">
-        <v>788.2</v>
+        <v>785.9</v>
       </c>
       <c r="M62" t="n">
-        <v>127.8</v>
+        <v>128.4</v>
       </c>
       <c r="N62" t="n">
         <v>288</v>
       </c>
       <c r="O62" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4348,47 +4376,47 @@
         <v>46270</v>
       </c>
       <c r="B63" t="n">
-        <v>178723.2</v>
+        <v>178722.5</v>
       </c>
       <c r="C63" t="n">
         <v>54205.7</v>
       </c>
       <c r="D63" t="n">
-        <v>5996.5</v>
+        <v>5999.7</v>
       </c>
       <c r="E63" t="n">
         <v>36141.7</v>
       </c>
       <c r="F63" t="n">
-        <v>17916.6</v>
+        <v>17915.6</v>
       </c>
       <c r="G63" t="n">
-        <v>4127.5</v>
+        <v>4127.2</v>
       </c>
       <c r="H63" t="n">
         <v>1615.6</v>
       </c>
       <c r="I63" t="n">
-        <v>29663</v>
+        <v>29661.8</v>
       </c>
       <c r="J63" t="n">
         <v>328389.7</v>
       </c>
       <c r="K63" t="n">
-        <v>29186.9</v>
+        <v>29185.1</v>
       </c>
       <c r="L63" t="n">
-        <v>402.8</v>
+        <v>403.4</v>
       </c>
       <c r="M63" t="n">
-        <v>73.2</v>
+        <v>73.3</v>
       </c>
       <c r="N63" t="n">
         <v>288</v>
       </c>
       <c r="O63" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4437,7 +4465,7 @@
       </c>
       <c r="O64" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4446,47 +4474,47 @@
         <v>46272</v>
       </c>
       <c r="B65" t="n">
-        <v>175392.1</v>
+        <v>175391.1</v>
       </c>
       <c r="C65" t="n">
         <v>57065.1</v>
       </c>
       <c r="D65" t="n">
-        <v>8451.299999999999</v>
+        <v>8452.700000000001</v>
       </c>
       <c r="E65" t="n">
-        <v>40111.8</v>
+        <v>40111.9</v>
       </c>
       <c r="F65" t="n">
-        <v>18170.3</v>
+        <v>18141.6</v>
       </c>
       <c r="G65" t="n">
-        <v>3322.1</v>
+        <v>3323.9</v>
       </c>
       <c r="H65" t="n">
         <v>1800.9</v>
       </c>
       <c r="I65" t="n">
-        <v>29681.6</v>
+        <v>29682.7</v>
       </c>
       <c r="J65" t="n">
-        <v>333995.1</v>
+        <v>333969.9</v>
       </c>
       <c r="K65" t="n">
-        <v>29220.9</v>
+        <v>29221.1</v>
       </c>
       <c r="L65" t="n">
-        <v>344.4</v>
+        <v>340.6</v>
       </c>
       <c r="M65" t="n">
-        <v>116.2</v>
+        <v>121.1</v>
       </c>
       <c r="N65" t="n">
         <v>288</v>
       </c>
       <c r="O65" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4504,38 +4532,38 @@
         <v>9369.6</v>
       </c>
       <c r="E66" t="n">
-        <v>41738.2</v>
+        <v>41738.3</v>
       </c>
       <c r="F66" t="n">
-        <v>20496</v>
+        <v>20494.4</v>
       </c>
       <c r="G66" t="n">
-        <v>1378.7</v>
+        <v>1377.9</v>
       </c>
       <c r="H66" t="n">
         <v>1798.2</v>
       </c>
       <c r="I66" t="n">
-        <v>29970.9</v>
+        <v>29971</v>
       </c>
       <c r="J66" t="n">
-        <v>337052.5</v>
+        <v>337050.4</v>
       </c>
       <c r="K66" t="n">
-        <v>29422.2</v>
+        <v>29421.6</v>
       </c>
       <c r="L66" t="n">
-        <v>435.7</v>
+        <v>434.3</v>
       </c>
       <c r="M66" t="n">
-        <v>113</v>
+        <v>115.1</v>
       </c>
       <c r="N66" t="n">
         <v>288</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4544,47 +4572,47 @@
         <v>46274</v>
       </c>
       <c r="B67" t="n">
-        <v>174154.5</v>
+        <v>174154.4</v>
       </c>
       <c r="C67" t="n">
         <v>57081.9</v>
       </c>
       <c r="D67" t="n">
-        <v>11630.6</v>
+        <v>11631.4</v>
       </c>
       <c r="E67" t="n">
-        <v>41389.9</v>
+        <v>41389.5</v>
       </c>
       <c r="F67" t="n">
-        <v>20323</v>
+        <v>20311.5</v>
       </c>
       <c r="G67" t="n">
-        <v>2013.2</v>
+        <v>2013.4</v>
       </c>
       <c r="H67" t="n">
         <v>1700</v>
       </c>
       <c r="I67" t="n">
-        <v>29743.2</v>
+        <v>29741.7</v>
       </c>
       <c r="J67" t="n">
-        <v>338036.3</v>
+        <v>338023.8</v>
       </c>
       <c r="K67" t="n">
-        <v>29164.9</v>
+        <v>29164.6</v>
       </c>
       <c r="L67" t="n">
-        <v>479.5</v>
+        <v>477.3</v>
       </c>
       <c r="M67" t="n">
-        <v>98.7</v>
+        <v>99.7</v>
       </c>
       <c r="N67" t="n">
         <v>288</v>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4593,47 +4621,47 @@
         <v>46275</v>
       </c>
       <c r="B68" t="n">
-        <v>171766.5</v>
+        <v>171766.4</v>
       </c>
       <c r="C68" t="n">
         <v>56394.2</v>
       </c>
       <c r="D68" t="n">
-        <v>10431.9</v>
+        <v>10435.1</v>
       </c>
       <c r="E68" t="n">
-        <v>42798.5</v>
+        <v>42798.6</v>
       </c>
       <c r="F68" t="n">
-        <v>22142.9</v>
+        <v>22145.8</v>
       </c>
       <c r="G68" t="n">
-        <v>2311.6</v>
+        <v>2311.5</v>
       </c>
       <c r="H68" t="n">
         <v>1815.8</v>
       </c>
       <c r="I68" t="n">
-        <v>29799.1</v>
+        <v>29795.2</v>
       </c>
       <c r="J68" t="n">
-        <v>337460.4</v>
+        <v>337462.6</v>
       </c>
       <c r="K68" t="n">
-        <v>29131</v>
+        <v>29130.4</v>
       </c>
       <c r="L68" t="n">
-        <v>578.6</v>
+        <v>573.1</v>
       </c>
       <c r="M68" t="n">
-        <v>89.40000000000001</v>
+        <v>91.7</v>
       </c>
       <c r="N68" t="n">
         <v>288</v>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4682,7 +4710,7 @@
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4691,19 +4719,19 @@
         <v>46277</v>
       </c>
       <c r="B70" t="n">
-        <v>169897.3</v>
+        <v>169897.1</v>
       </c>
       <c r="C70" t="n">
         <v>54039</v>
       </c>
       <c r="D70" t="n">
-        <v>7329.9</v>
+        <v>7332.3</v>
       </c>
       <c r="E70" t="n">
-        <v>42362.4</v>
+        <v>42362.5</v>
       </c>
       <c r="F70" t="n">
-        <v>24898.8</v>
+        <v>24895.1</v>
       </c>
       <c r="G70" t="n">
         <v>111.4</v>
@@ -4712,26 +4740,26 @@
         <v>1875</v>
       </c>
       <c r="I70" t="n">
-        <v>28386.3</v>
+        <v>28386.5</v>
       </c>
       <c r="J70" t="n">
-        <v>328900.1</v>
+        <v>328898.8</v>
       </c>
       <c r="K70" t="n">
-        <v>27909.5</v>
+        <v>27909.4</v>
       </c>
       <c r="L70" t="n">
-        <v>388.3</v>
+        <v>387.5</v>
       </c>
       <c r="M70" t="n">
-        <v>88.5</v>
+        <v>89.5</v>
       </c>
       <c r="N70" t="n">
         <v>288</v>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4780,7 +4808,7 @@
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4789,47 +4817,47 @@
         <v>46279</v>
       </c>
       <c r="B72" t="n">
-        <v>178146.7</v>
+        <v>178146.4</v>
       </c>
       <c r="C72" t="n">
         <v>56156.7</v>
       </c>
       <c r="D72" t="n">
-        <v>6117.3</v>
+        <v>6120.9</v>
       </c>
       <c r="E72" t="n">
-        <v>44097.2</v>
+        <v>44097.3</v>
       </c>
       <c r="F72" t="n">
-        <v>33190.8</v>
+        <v>33195.3</v>
       </c>
       <c r="G72" t="n">
-        <v>2220.7</v>
+        <v>2220.5</v>
       </c>
       <c r="H72" t="n">
         <v>1737.1</v>
       </c>
       <c r="I72" t="n">
-        <v>28808.8</v>
+        <v>28807.2</v>
       </c>
       <c r="J72" t="n">
-        <v>350475.3</v>
+        <v>350481.5</v>
       </c>
       <c r="K72" t="n">
-        <v>28499.5</v>
+        <v>28497</v>
       </c>
       <c r="L72" t="n">
-        <v>227.4</v>
+        <v>224.4</v>
       </c>
       <c r="M72" t="n">
-        <v>82</v>
+        <v>85.8</v>
       </c>
       <c r="N72" t="n">
         <v>288</v>
       </c>
       <c r="O72" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4844,41 +4872,41 @@
         <v>57124.4</v>
       </c>
       <c r="D73" t="n">
-        <v>6486.8</v>
+        <v>6488.5</v>
       </c>
       <c r="E73" t="n">
-        <v>36835.6</v>
+        <v>36835.5</v>
       </c>
       <c r="F73" t="n">
-        <v>29747.4</v>
+        <v>29746.3</v>
       </c>
       <c r="G73" t="n">
-        <v>3732.7</v>
+        <v>3732.9</v>
       </c>
       <c r="H73" t="n">
-        <v>1769.6</v>
+        <v>1769.7</v>
       </c>
       <c r="I73" t="n">
-        <v>31390</v>
+        <v>31390.4</v>
       </c>
       <c r="J73" t="n">
-        <v>358758.8</v>
+        <v>358759.6</v>
       </c>
       <c r="K73" t="n">
         <v>30075.9</v>
       </c>
       <c r="L73" t="n">
-        <v>1196.3</v>
+        <v>1194.2</v>
       </c>
       <c r="M73" t="n">
-        <v>117.8</v>
+        <v>120.3</v>
       </c>
       <c r="N73" t="n">
         <v>288</v>
       </c>
       <c r="O73" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4927,7 +4955,7 @@
       </c>
       <c r="O74" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -4976,7 +5004,7 @@
       </c>
       <c r="O75" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5025,7 +5053,7 @@
       </c>
       <c r="O76" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5074,7 +5102,7 @@
       </c>
       <c r="O77" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5123,7 +5151,7 @@
       </c>
       <c r="O78" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5132,47 +5160,47 @@
         <v>46286</v>
       </c>
       <c r="B79" t="n">
-        <v>187076.4</v>
+        <v>187061.8</v>
       </c>
       <c r="C79" t="n">
         <v>67566.60000000001</v>
       </c>
       <c r="D79" t="n">
-        <v>6849.9</v>
+        <v>6872.2</v>
       </c>
       <c r="E79" t="n">
         <v>39105.3</v>
       </c>
       <c r="F79" t="n">
-        <v>31106.3</v>
+        <v>31067</v>
       </c>
       <c r="G79" t="n">
-        <v>1014</v>
+        <v>1013.4</v>
       </c>
       <c r="H79" t="n">
         <v>1814.6</v>
       </c>
       <c r="I79" t="n">
-        <v>29674.7</v>
+        <v>29685.8</v>
       </c>
       <c r="J79" t="n">
-        <v>364207.7</v>
+        <v>364186.6</v>
       </c>
       <c r="K79" t="n">
-        <v>29331.4</v>
+        <v>29333.3</v>
       </c>
       <c r="L79" t="n">
-        <v>260.1</v>
+        <v>265.7</v>
       </c>
       <c r="M79" t="n">
-        <v>83.2</v>
+        <v>86.8</v>
       </c>
       <c r="N79" t="n">
         <v>288</v>
       </c>
       <c r="O79" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5249,7 @@
       </c>
       <c r="O80" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5230,19 +5258,19 @@
         <v>46288</v>
       </c>
       <c r="B81" t="n">
-        <v>195329.6</v>
+        <v>195328</v>
       </c>
       <c r="C81" t="n">
         <v>64371.5</v>
       </c>
       <c r="D81" t="n">
-        <v>5132.1</v>
+        <v>5149.6</v>
       </c>
       <c r="E81" t="n">
         <v>38402.5</v>
       </c>
       <c r="F81" t="n">
-        <v>29887</v>
+        <v>29880</v>
       </c>
       <c r="G81" t="n">
         <v>1023.3</v>
@@ -5251,26 +5279,26 @@
         <v>1786.6</v>
       </c>
       <c r="I81" t="n">
-        <v>29679.5</v>
+        <v>29678.4</v>
       </c>
       <c r="J81" t="n">
-        <v>365612.1</v>
+        <v>365620.1</v>
       </c>
       <c r="K81" t="n">
-        <v>29467.5</v>
+        <v>29468</v>
       </c>
       <c r="L81" t="n">
-        <v>138.4</v>
+        <v>136.6</v>
       </c>
       <c r="M81" t="n">
-        <v>73.5</v>
+        <v>73.90000000000001</v>
       </c>
       <c r="N81" t="n">
         <v>288</v>
       </c>
       <c r="O81" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5319,7 +5347,7 @@
       </c>
       <c r="O82" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5396,7 @@
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>DIPCER</t>
+          <t>DIPCEF</t>
         </is>
       </c>
     </row>
@@ -5759,6 +5787,1182 @@
         <v>288</v>
       </c>
       <c r="O91" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B92" t="n">
+        <v>179768.2</v>
+      </c>
+      <c r="C92" t="n">
+        <v>52554</v>
+      </c>
+      <c r="D92" t="n">
+        <v>882.7</v>
+      </c>
+      <c r="E92" t="n">
+        <v>36758</v>
+      </c>
+      <c r="F92" t="n">
+        <v>31692.4</v>
+      </c>
+      <c r="G92" t="n">
+        <v>631.3</v>
+      </c>
+      <c r="H92" t="n">
+        <v>3083.8</v>
+      </c>
+      <c r="I92" t="n">
+        <v>29680.7</v>
+      </c>
+      <c r="J92" t="n">
+        <v>335051</v>
+      </c>
+      <c r="K92" t="n">
+        <v>29518.4</v>
+      </c>
+      <c r="L92" t="n">
+        <v>90.09999999999999</v>
+      </c>
+      <c r="M92" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N92" t="n">
+        <v>288</v>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B93" t="n">
+        <v>197139.9</v>
+      </c>
+      <c r="C93" t="n">
+        <v>62271.7</v>
+      </c>
+      <c r="D93" t="n">
+        <v>3745.1</v>
+      </c>
+      <c r="E93" t="n">
+        <v>36155.3</v>
+      </c>
+      <c r="F93" t="n">
+        <v>32114.7</v>
+      </c>
+      <c r="G93" t="n">
+        <v>1400.1</v>
+      </c>
+      <c r="H93" t="n">
+        <v>3007.7</v>
+      </c>
+      <c r="I93" t="n">
+        <v>29147.9</v>
+      </c>
+      <c r="J93" t="n">
+        <v>364982.2</v>
+      </c>
+      <c r="K93" t="n">
+        <v>28870.1</v>
+      </c>
+      <c r="L93" t="n">
+        <v>205.6</v>
+      </c>
+      <c r="M93" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N93" t="n">
+        <v>288</v>
+      </c>
+      <c r="O93" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B94" t="n">
+        <v>192697</v>
+      </c>
+      <c r="C94" t="n">
+        <v>67354.3</v>
+      </c>
+      <c r="D94" t="n">
+        <v>3424.9</v>
+      </c>
+      <c r="E94" t="n">
+        <v>37539.1</v>
+      </c>
+      <c r="F94" t="n">
+        <v>32522.8</v>
+      </c>
+      <c r="G94" t="n">
+        <v>1463.7</v>
+      </c>
+      <c r="H94" t="n">
+        <v>2708.2</v>
+      </c>
+      <c r="I94" t="n">
+        <v>29512.1</v>
+      </c>
+      <c r="J94" t="n">
+        <v>367222.2</v>
+      </c>
+      <c r="K94" t="n">
+        <v>29316.6</v>
+      </c>
+      <c r="L94" t="n">
+        <v>123.4</v>
+      </c>
+      <c r="M94" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N94" t="n">
+        <v>288</v>
+      </c>
+      <c r="O94" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B95" t="n">
+        <v>193424.1</v>
+      </c>
+      <c r="C95" t="n">
+        <v>66600.8</v>
+      </c>
+      <c r="D95" t="n">
+        <v>2486.5</v>
+      </c>
+      <c r="E95" t="n">
+        <v>35050.2</v>
+      </c>
+      <c r="F95" t="n">
+        <v>33917.1</v>
+      </c>
+      <c r="G95" t="n">
+        <v>4433</v>
+      </c>
+      <c r="H95" t="n">
+        <v>2594.1</v>
+      </c>
+      <c r="I95" t="n">
+        <v>29597.9</v>
+      </c>
+      <c r="J95" t="n">
+        <v>368103.7</v>
+      </c>
+      <c r="K95" t="n">
+        <v>29446.5</v>
+      </c>
+      <c r="L95" t="n">
+        <v>79.2</v>
+      </c>
+      <c r="M95" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N95" t="n">
+        <v>288</v>
+      </c>
+      <c r="O95" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B96" t="n">
+        <v>191696.1</v>
+      </c>
+      <c r="C96" t="n">
+        <v>67882.5</v>
+      </c>
+      <c r="D96" t="n">
+        <v>1741.2</v>
+      </c>
+      <c r="E96" t="n">
+        <v>35058.2</v>
+      </c>
+      <c r="F96" t="n">
+        <v>28227.9</v>
+      </c>
+      <c r="G96" t="n">
+        <v>5598.1</v>
+      </c>
+      <c r="H96" t="n">
+        <v>2695.4</v>
+      </c>
+      <c r="I96" t="n">
+        <v>29512.9</v>
+      </c>
+      <c r="J96" t="n">
+        <v>362412.2</v>
+      </c>
+      <c r="K96" t="n">
+        <v>29355</v>
+      </c>
+      <c r="L96" t="n">
+        <v>85.7</v>
+      </c>
+      <c r="M96" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N96" t="n">
+        <v>288</v>
+      </c>
+      <c r="O96" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B97" t="n">
+        <v>191433.1</v>
+      </c>
+      <c r="C97" t="n">
+        <v>61182</v>
+      </c>
+      <c r="D97" t="n">
+        <v>2587.5</v>
+      </c>
+      <c r="E97" t="n">
+        <v>34856.3</v>
+      </c>
+      <c r="F97" t="n">
+        <v>33300.3</v>
+      </c>
+      <c r="G97" t="n">
+        <v>3910.3</v>
+      </c>
+      <c r="H97" t="n">
+        <v>2651.4</v>
+      </c>
+      <c r="I97" t="n">
+        <v>29046.9</v>
+      </c>
+      <c r="J97" t="n">
+        <v>358967.7</v>
+      </c>
+      <c r="K97" t="n">
+        <v>28791.5</v>
+      </c>
+      <c r="L97" t="n">
+        <v>183.2</v>
+      </c>
+      <c r="M97" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N97" t="n">
+        <v>288</v>
+      </c>
+      <c r="O97" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B98" t="n">
+        <v>181528.7</v>
+      </c>
+      <c r="C98" t="n">
+        <v>62603.9</v>
+      </c>
+      <c r="D98" t="n">
+        <v>1887.2</v>
+      </c>
+      <c r="E98" t="n">
+        <v>34725.4</v>
+      </c>
+      <c r="F98" t="n">
+        <v>30868</v>
+      </c>
+      <c r="G98" t="n">
+        <v>4103.8</v>
+      </c>
+      <c r="H98" t="n">
+        <v>2811.6</v>
+      </c>
+      <c r="I98" t="n">
+        <v>28265</v>
+      </c>
+      <c r="J98" t="n">
+        <v>346793.5</v>
+      </c>
+      <c r="K98" t="n">
+        <v>28099</v>
+      </c>
+      <c r="L98" t="n">
+        <v>93.8</v>
+      </c>
+      <c r="M98" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N98" t="n">
+        <v>288</v>
+      </c>
+      <c r="O98" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B99" t="n">
+        <v>177116.8</v>
+      </c>
+      <c r="C99" t="n">
+        <v>52673.4</v>
+      </c>
+      <c r="D99" t="n">
+        <v>1651</v>
+      </c>
+      <c r="E99" t="n">
+        <v>30940.4</v>
+      </c>
+      <c r="F99" t="n">
+        <v>24056.8</v>
+      </c>
+      <c r="G99" t="n">
+        <v>4903</v>
+      </c>
+      <c r="H99" t="n">
+        <v>2918.6</v>
+      </c>
+      <c r="I99" t="n">
+        <v>27637.7</v>
+      </c>
+      <c r="J99" t="n">
+        <v>321897.6</v>
+      </c>
+      <c r="K99" t="n">
+        <v>27498.2</v>
+      </c>
+      <c r="L99" t="n">
+        <v>67.3</v>
+      </c>
+      <c r="M99" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N99" t="n">
+        <v>288</v>
+      </c>
+      <c r="O99" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B100" t="n">
+        <v>192097.4</v>
+      </c>
+      <c r="C100" t="n">
+        <v>58714.1</v>
+      </c>
+      <c r="D100" t="n">
+        <v>3354.8</v>
+      </c>
+      <c r="E100" t="n">
+        <v>34713.2</v>
+      </c>
+      <c r="F100" t="n">
+        <v>28986</v>
+      </c>
+      <c r="G100" t="n">
+        <v>4810.5</v>
+      </c>
+      <c r="H100" t="n">
+        <v>2656.2</v>
+      </c>
+      <c r="I100" t="n">
+        <v>28448.5</v>
+      </c>
+      <c r="J100" t="n">
+        <v>353780.7</v>
+      </c>
+      <c r="K100" t="n">
+        <v>28200.2</v>
+      </c>
+      <c r="L100" t="n">
+        <v>176.1</v>
+      </c>
+      <c r="M100" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N100" t="n">
+        <v>288</v>
+      </c>
+      <c r="O100" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B101" t="n">
+        <v>189867.4</v>
+      </c>
+      <c r="C101" t="n">
+        <v>71270.39999999999</v>
+      </c>
+      <c r="D101" t="n">
+        <v>4619.1</v>
+      </c>
+      <c r="E101" t="n">
+        <v>33106.7</v>
+      </c>
+      <c r="F101" t="n">
+        <v>30565.1</v>
+      </c>
+      <c r="G101" t="n">
+        <v>2986.6</v>
+      </c>
+      <c r="H101" t="n">
+        <v>2683.8</v>
+      </c>
+      <c r="I101" t="n">
+        <v>28057</v>
+      </c>
+      <c r="J101" t="n">
+        <v>363156.1</v>
+      </c>
+      <c r="K101" t="n">
+        <v>27818.3</v>
+      </c>
+      <c r="L101" t="n">
+        <v>166.6</v>
+      </c>
+      <c r="M101" t="n">
+        <v>72.2</v>
+      </c>
+      <c r="N101" t="n">
+        <v>288</v>
+      </c>
+      <c r="O101" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B102" t="n">
+        <v>193693.9</v>
+      </c>
+      <c r="C102" t="n">
+        <v>64393.6</v>
+      </c>
+      <c r="D102" t="n">
+        <v>2756.3</v>
+      </c>
+      <c r="E102" t="n">
+        <v>32864</v>
+      </c>
+      <c r="F102" t="n">
+        <v>32537.2</v>
+      </c>
+      <c r="G102" t="n">
+        <v>4817.3</v>
+      </c>
+      <c r="H102" t="n">
+        <v>2929.1</v>
+      </c>
+      <c r="I102" t="n">
+        <v>28124.4</v>
+      </c>
+      <c r="J102" t="n">
+        <v>362115.8</v>
+      </c>
+      <c r="K102" t="n">
+        <v>26216.7</v>
+      </c>
+      <c r="L102" t="n">
+        <v>266.2</v>
+      </c>
+      <c r="M102" t="n">
+        <v>1641.5</v>
+      </c>
+      <c r="N102" t="n">
+        <v>288</v>
+      </c>
+      <c r="O102" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B103" t="n">
+        <v>194964.8</v>
+      </c>
+      <c r="C103" t="n">
+        <v>59790.2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>4644.6</v>
+      </c>
+      <c r="E103" t="n">
+        <v>33046.6</v>
+      </c>
+      <c r="F103" t="n">
+        <v>36043.9</v>
+      </c>
+      <c r="G103" t="n">
+        <v>3966.6</v>
+      </c>
+      <c r="H103" t="n">
+        <v>2908.2</v>
+      </c>
+      <c r="I103" t="n">
+        <v>28123.8</v>
+      </c>
+      <c r="J103" t="n">
+        <v>363488.7</v>
+      </c>
+      <c r="K103" t="n">
+        <v>25994.1</v>
+      </c>
+      <c r="L103" t="n">
+        <v>322.3</v>
+      </c>
+      <c r="M103" t="n">
+        <v>1807.4</v>
+      </c>
+      <c r="N103" t="n">
+        <v>288</v>
+      </c>
+      <c r="O103" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B104" t="n">
+        <v>203972.4</v>
+      </c>
+      <c r="C104" t="n">
+        <v>56831.9</v>
+      </c>
+      <c r="D104" t="n">
+        <v>4209.9</v>
+      </c>
+      <c r="E104" t="n">
+        <v>29460.2</v>
+      </c>
+      <c r="F104" t="n">
+        <v>32914.9</v>
+      </c>
+      <c r="G104" t="n">
+        <v>3793.2</v>
+      </c>
+      <c r="H104" t="n">
+        <v>3008.8</v>
+      </c>
+      <c r="I104" t="n">
+        <v>28609.8</v>
+      </c>
+      <c r="J104" t="n">
+        <v>362801.1</v>
+      </c>
+      <c r="K104" t="n">
+        <v>26519.3</v>
+      </c>
+      <c r="L104" t="n">
+        <v>344.2</v>
+      </c>
+      <c r="M104" t="n">
+        <v>1746.4</v>
+      </c>
+      <c r="N104" t="n">
+        <v>288</v>
+      </c>
+      <c r="O104" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B105" t="n">
+        <v>196518.9</v>
+      </c>
+      <c r="C105" t="n">
+        <v>60618.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>3839.4</v>
+      </c>
+      <c r="E105" t="n">
+        <v>27671.6</v>
+      </c>
+      <c r="F105" t="n">
+        <v>27088.1</v>
+      </c>
+      <c r="G105" t="n">
+        <v>4852.4</v>
+      </c>
+      <c r="H105" t="n">
+        <v>3012.3</v>
+      </c>
+      <c r="I105" t="n">
+        <v>28811.1</v>
+      </c>
+      <c r="J105" t="n">
+        <v>352412</v>
+      </c>
+      <c r="K105" t="n">
+        <v>26777.5</v>
+      </c>
+      <c r="L105" t="n">
+        <v>309.8</v>
+      </c>
+      <c r="M105" t="n">
+        <v>1723.8</v>
+      </c>
+      <c r="N105" t="n">
+        <v>288</v>
+      </c>
+      <c r="O105" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B106" t="n">
+        <v>186417.5</v>
+      </c>
+      <c r="C106" t="n">
+        <v>50772.2</v>
+      </c>
+      <c r="D106" t="n">
+        <v>2425.1</v>
+      </c>
+      <c r="E106" t="n">
+        <v>27990.8</v>
+      </c>
+      <c r="F106" t="n">
+        <v>30248.4</v>
+      </c>
+      <c r="G106" t="n">
+        <v>4437.9</v>
+      </c>
+      <c r="H106" t="n">
+        <v>3027.3</v>
+      </c>
+      <c r="I106" t="n">
+        <v>28589.5</v>
+      </c>
+      <c r="J106" t="n">
+        <v>333908.8</v>
+      </c>
+      <c r="K106" t="n">
+        <v>26760.2</v>
+      </c>
+      <c r="L106" t="n">
+        <v>141.5</v>
+      </c>
+      <c r="M106" t="n">
+        <v>1687.8</v>
+      </c>
+      <c r="N106" t="n">
+        <v>288</v>
+      </c>
+      <c r="O106" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B107" t="n">
+        <v>200885.4</v>
+      </c>
+      <c r="C107" t="n">
+        <v>55179.1</v>
+      </c>
+      <c r="D107" t="n">
+        <v>6266.6</v>
+      </c>
+      <c r="E107" t="n">
+        <v>36328.3</v>
+      </c>
+      <c r="F107" t="n">
+        <v>33040</v>
+      </c>
+      <c r="G107" t="n">
+        <v>4514.6</v>
+      </c>
+      <c r="H107" t="n">
+        <v>2807.8</v>
+      </c>
+      <c r="I107" t="n">
+        <v>28687.5</v>
+      </c>
+      <c r="J107" t="n">
+        <v>367709.2</v>
+      </c>
+      <c r="K107" t="n">
+        <v>26627.8</v>
+      </c>
+      <c r="L107" t="n">
+        <v>314</v>
+      </c>
+      <c r="M107" t="n">
+        <v>1745.7</v>
+      </c>
+      <c r="N107" t="n">
+        <v>288</v>
+      </c>
+      <c r="O107" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B108" t="n">
+        <v>208600.4</v>
+      </c>
+      <c r="C108" t="n">
+        <v>59978.7</v>
+      </c>
+      <c r="D108" t="n">
+        <v>5909.4</v>
+      </c>
+      <c r="E108" t="n">
+        <v>33188.6</v>
+      </c>
+      <c r="F108" t="n">
+        <v>34512.9</v>
+      </c>
+      <c r="G108" t="n">
+        <v>4142.7</v>
+      </c>
+      <c r="H108" t="n">
+        <v>2975.4</v>
+      </c>
+      <c r="I108" t="n">
+        <v>29550.5</v>
+      </c>
+      <c r="J108" t="n">
+        <v>378858.6</v>
+      </c>
+      <c r="K108" t="n">
+        <v>27455.4</v>
+      </c>
+      <c r="L108" t="n">
+        <v>363.5</v>
+      </c>
+      <c r="M108" t="n">
+        <v>1731.5</v>
+      </c>
+      <c r="N108" t="n">
+        <v>288</v>
+      </c>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B109" t="n">
+        <v>216274.4</v>
+      </c>
+      <c r="C109" t="n">
+        <v>65280.2</v>
+      </c>
+      <c r="D109" t="n">
+        <v>5265.9</v>
+      </c>
+      <c r="E109" t="n">
+        <v>27905.3</v>
+      </c>
+      <c r="F109" t="n">
+        <v>34662.8</v>
+      </c>
+      <c r="G109" t="n">
+        <v>4205</v>
+      </c>
+      <c r="H109" t="n">
+        <v>3051.7</v>
+      </c>
+      <c r="I109" t="n">
+        <v>30066.1</v>
+      </c>
+      <c r="J109" t="n">
+        <v>386711.3</v>
+      </c>
+      <c r="K109" t="n">
+        <v>27974.5</v>
+      </c>
+      <c r="L109" t="n">
+        <v>322</v>
+      </c>
+      <c r="M109" t="n">
+        <v>1769.6</v>
+      </c>
+      <c r="N109" t="n">
+        <v>288</v>
+      </c>
+      <c r="O109" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B110" t="n">
+        <v>211130.2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>69785.5</v>
+      </c>
+      <c r="D110" t="n">
+        <v>7253.6</v>
+      </c>
+      <c r="E110" t="n">
+        <v>29602.6</v>
+      </c>
+      <c r="F110" t="n">
+        <v>28796.2</v>
+      </c>
+      <c r="G110" t="n">
+        <v>4900.2</v>
+      </c>
+      <c r="H110" t="n">
+        <v>3082.4</v>
+      </c>
+      <c r="I110" t="n">
+        <v>29702.4</v>
+      </c>
+      <c r="J110" t="n">
+        <v>384253.2</v>
+      </c>
+      <c r="K110" t="n">
+        <v>27766.7</v>
+      </c>
+      <c r="L110" t="n">
+        <v>295.7</v>
+      </c>
+      <c r="M110" t="n">
+        <v>1640</v>
+      </c>
+      <c r="N110" t="n">
+        <v>288</v>
+      </c>
+      <c r="O110" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B111" t="n">
+        <v>214919.2</v>
+      </c>
+      <c r="C111" t="n">
+        <v>63997.5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>3801.1</v>
+      </c>
+      <c r="E111" t="n">
+        <v>26958.8</v>
+      </c>
+      <c r="F111" t="n">
+        <v>25433</v>
+      </c>
+      <c r="G111" t="n">
+        <v>5033.1</v>
+      </c>
+      <c r="H111" t="n">
+        <v>3232.2</v>
+      </c>
+      <c r="I111" t="n">
+        <v>28844.6</v>
+      </c>
+      <c r="J111" t="n">
+        <v>372219.6</v>
+      </c>
+      <c r="K111" t="n">
+        <v>27116.3</v>
+      </c>
+      <c r="L111" t="n">
+        <v>244.5</v>
+      </c>
+      <c r="M111" t="n">
+        <v>1483.8</v>
+      </c>
+      <c r="N111" t="n">
+        <v>288</v>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B112" t="n">
+        <v>210535.3</v>
+      </c>
+      <c r="C112" t="n">
+        <v>54939.1</v>
+      </c>
+      <c r="D112" t="n">
+        <v>1989.1</v>
+      </c>
+      <c r="E112" t="n">
+        <v>25088</v>
+      </c>
+      <c r="F112" t="n">
+        <v>25731.2</v>
+      </c>
+      <c r="G112" t="n">
+        <v>3046.6</v>
+      </c>
+      <c r="H112" t="n">
+        <v>3235.1</v>
+      </c>
+      <c r="I112" t="n">
+        <v>28693.9</v>
+      </c>
+      <c r="J112" t="n">
+        <v>353258.3</v>
+      </c>
+      <c r="K112" t="n">
+        <v>27005.3</v>
+      </c>
+      <c r="L112" t="n">
+        <v>108.5</v>
+      </c>
+      <c r="M112" t="n">
+        <v>1580.1</v>
+      </c>
+      <c r="N112" t="n">
+        <v>288</v>
+      </c>
+      <c r="O112" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B113" t="n">
+        <v>195892.9</v>
+      </c>
+      <c r="C113" t="n">
+        <v>52465.3</v>
+      </c>
+      <c r="D113" t="n">
+        <v>1025.9</v>
+      </c>
+      <c r="E113" t="n">
+        <v>22519.8</v>
+      </c>
+      <c r="F113" t="n">
+        <v>29756</v>
+      </c>
+      <c r="G113" t="n">
+        <v>386.4</v>
+      </c>
+      <c r="H113" t="n">
+        <v>3070.6</v>
+      </c>
+      <c r="I113" t="n">
+        <v>28988.5</v>
+      </c>
+      <c r="J113" t="n">
+        <v>334105.2</v>
+      </c>
+      <c r="K113" t="n">
+        <v>27214.5</v>
+      </c>
+      <c r="L113" t="n">
+        <v>108.3</v>
+      </c>
+      <c r="M113" t="n">
+        <v>1665.7</v>
+      </c>
+      <c r="N113" t="n">
+        <v>288</v>
+      </c>
+      <c r="O113" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B114" t="n">
+        <v>206582.6</v>
+      </c>
+      <c r="C114" t="n">
+        <v>58757.7</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5032.3</v>
+      </c>
+      <c r="E114" t="n">
+        <v>28288.7</v>
+      </c>
+      <c r="F114" t="n">
+        <v>34556</v>
+      </c>
+      <c r="G114" t="n">
+        <v>3264.5</v>
+      </c>
+      <c r="H114" t="n">
+        <v>2721</v>
+      </c>
+      <c r="I114" t="n">
+        <v>29588.1</v>
+      </c>
+      <c r="J114" t="n">
+        <v>368790.9</v>
+      </c>
+      <c r="K114" t="n">
+        <v>27473</v>
+      </c>
+      <c r="L114" t="n">
+        <v>393.5</v>
+      </c>
+      <c r="M114" t="n">
+        <v>1721.6</v>
+      </c>
+      <c r="N114" t="n">
+        <v>288</v>
+      </c>
+      <c r="O114" t="inlineStr">
+        <is>
+          <t>DIPCER</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B115" t="n">
+        <v>216758.4</v>
+      </c>
+      <c r="C115" t="n">
+        <v>56753.8</v>
+      </c>
+      <c r="D115" t="n">
+        <v>6666.6</v>
+      </c>
+      <c r="E115" t="n">
+        <v>25873.4</v>
+      </c>
+      <c r="F115" t="n">
+        <v>33528.9</v>
+      </c>
+      <c r="G115" t="n">
+        <v>5409.8</v>
+      </c>
+      <c r="H115" t="n">
+        <v>3026.3</v>
+      </c>
+      <c r="I115" t="n">
+        <v>29535</v>
+      </c>
+      <c r="J115" t="n">
+        <v>377552.1</v>
+      </c>
+      <c r="K115" t="n">
+        <v>27342.3</v>
+      </c>
+      <c r="L115" t="n">
+        <v>494.4</v>
+      </c>
+      <c r="M115" t="n">
+        <v>1698.3</v>
+      </c>
+      <c r="N115" t="n">
+        <v>288</v>
+      </c>
+      <c r="O115" t="inlineStr">
         <is>
           <t>DIPCER</t>
         </is>
@@ -5775,7 +6979,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D92"/>
+  <dimension ref="A1:D116"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -7074,6 +8278,342 @@
         <v>341685.1</v>
       </c>
     </row>
+    <row r="93">
+      <c r="A93" s="4" t="n">
+        <v>46299</v>
+      </c>
+      <c r="B93" t="n">
+        <v>13475.7</v>
+      </c>
+      <c r="C93" t="n">
+        <v>15447.8</v>
+      </c>
+      <c r="D93" t="n">
+        <v>323417</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="4" t="n">
+        <v>46300</v>
+      </c>
+      <c r="B94" t="n">
+        <v>14887.5</v>
+      </c>
+      <c r="C94" t="n">
+        <v>17631.6</v>
+      </c>
+      <c r="D94" t="n">
+        <v>357299</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="n">
+        <v>46301</v>
+      </c>
+      <c r="B95" t="n">
+        <v>14849.5</v>
+      </c>
+      <c r="C95" t="n">
+        <v>17432.8</v>
+      </c>
+      <c r="D95" t="n">
+        <v>356389</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="4" t="n">
+        <v>46302</v>
+      </c>
+      <c r="B96" t="n">
+        <v>14872</v>
+      </c>
+      <c r="C96" t="n">
+        <v>17101.3</v>
+      </c>
+      <c r="D96" t="n">
+        <v>356928.5</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="4" t="n">
+        <v>46303</v>
+      </c>
+      <c r="B97" t="n">
+        <v>14609.3</v>
+      </c>
+      <c r="C97" t="n">
+        <v>16695.6</v>
+      </c>
+      <c r="D97" t="n">
+        <v>350624.1</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="4" t="n">
+        <v>46304</v>
+      </c>
+      <c r="B98" t="n">
+        <v>14550.1</v>
+      </c>
+      <c r="C98" t="n">
+        <v>16660</v>
+      </c>
+      <c r="D98" t="n">
+        <v>349203.5</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="4" t="n">
+        <v>46305</v>
+      </c>
+      <c r="B99" t="n">
+        <v>14045.3</v>
+      </c>
+      <c r="C99" t="n">
+        <v>15915.7</v>
+      </c>
+      <c r="D99" t="n">
+        <v>337086.2</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="4" t="n">
+        <v>46306</v>
+      </c>
+      <c r="B100" t="n">
+        <v>13011.6</v>
+      </c>
+      <c r="C100" t="n">
+        <v>14935.5</v>
+      </c>
+      <c r="D100" t="n">
+        <v>312278</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="4" t="n">
+        <v>46307</v>
+      </c>
+      <c r="B101" t="n">
+        <v>14336</v>
+      </c>
+      <c r="C101" t="n">
+        <v>16758</v>
+      </c>
+      <c r="D101" t="n">
+        <v>344064.3</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="4" t="n">
+        <v>46308</v>
+      </c>
+      <c r="B102" t="n">
+        <v>14701.8</v>
+      </c>
+      <c r="C102" t="n">
+        <v>16837.9</v>
+      </c>
+      <c r="D102" t="n">
+        <v>352843.3</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="4" t="n">
+        <v>46309</v>
+      </c>
+      <c r="B103" t="n">
+        <v>14696.8</v>
+      </c>
+      <c r="C103" t="n">
+        <v>16732.2</v>
+      </c>
+      <c r="D103" t="n">
+        <v>352722.3</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="4" t="n">
+        <v>46310</v>
+      </c>
+      <c r="B104" t="n">
+        <v>14761.7</v>
+      </c>
+      <c r="C104" t="n">
+        <v>17021.6</v>
+      </c>
+      <c r="D104" t="n">
+        <v>354280.3</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="4" t="n">
+        <v>46311</v>
+      </c>
+      <c r="B105" t="n">
+        <v>14730.5</v>
+      </c>
+      <c r="C105" t="n">
+        <v>16738.1</v>
+      </c>
+      <c r="D105" t="n">
+        <v>353531.8</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="4" t="n">
+        <v>46312</v>
+      </c>
+      <c r="B106" t="n">
+        <v>14259.4</v>
+      </c>
+      <c r="C106" t="n">
+        <v>16074.8</v>
+      </c>
+      <c r="D106" t="n">
+        <v>342224.6</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="4" t="n">
+        <v>46313</v>
+      </c>
+      <c r="B107" t="n">
+        <v>13451.9</v>
+      </c>
+      <c r="C107" t="n">
+        <v>15403.8</v>
+      </c>
+      <c r="D107" t="n">
+        <v>322844.9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="4" t="n">
+        <v>46314</v>
+      </c>
+      <c r="B108" t="n">
+        <v>14960.2</v>
+      </c>
+      <c r="C108" t="n">
+        <v>17343.8</v>
+      </c>
+      <c r="D108" t="n">
+        <v>359045.4</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="4" t="n">
+        <v>46315</v>
+      </c>
+      <c r="B109" t="n">
+        <v>15387.5</v>
+      </c>
+      <c r="C109" t="n">
+        <v>17924.4</v>
+      </c>
+      <c r="D109" t="n">
+        <v>369300.2</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="4" t="n">
+        <v>46316</v>
+      </c>
+      <c r="B110" t="n">
+        <v>15699.2</v>
+      </c>
+      <c r="C110" t="n">
+        <v>18097.8</v>
+      </c>
+      <c r="D110" t="n">
+        <v>376780.3</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="4" t="n">
+        <v>46317</v>
+      </c>
+      <c r="B111" t="n">
+        <v>15602.5</v>
+      </c>
+      <c r="C111" t="n">
+        <v>17871</v>
+      </c>
+      <c r="D111" t="n">
+        <v>374460.3</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="4" t="n">
+        <v>46318</v>
+      </c>
+      <c r="B112" t="n">
+        <v>15099</v>
+      </c>
+      <c r="C112" t="n">
+        <v>16880.6</v>
+      </c>
+      <c r="D112" t="n">
+        <v>362375.8</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="4" t="n">
+        <v>46319</v>
+      </c>
+      <c r="B113" t="n">
+        <v>14262.1</v>
+      </c>
+      <c r="C113" t="n">
+        <v>15982.5</v>
+      </c>
+      <c r="D113" t="n">
+        <v>342289.7</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="4" t="n">
+        <v>46320</v>
+      </c>
+      <c r="B114" t="n">
+        <v>13394</v>
+      </c>
+      <c r="C114" t="n">
+        <v>15261.8</v>
+      </c>
+      <c r="D114" t="n">
+        <v>321456.1</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="4" t="n">
+        <v>46321</v>
+      </c>
+      <c r="B115" t="n">
+        <v>14973.7</v>
+      </c>
+      <c r="C115" t="n">
+        <v>17621.2</v>
+      </c>
+      <c r="D115" t="n">
+        <v>359369</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="4" t="n">
+        <v>46322</v>
+      </c>
+      <c r="B116" t="n">
+        <v>15270.5</v>
+      </c>
+      <c r="C116" t="n">
+        <v>17836.1</v>
+      </c>
+      <c r="D116" t="n">
+        <v>366492.3</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
